--- a/output/tables/risk_dashboard.xlsx
+++ b/output/tables/risk_dashboard.xlsx
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>76.1%</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.11x</t>
+          <t>0.10x</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.59x</t>
+          <t>0.53x</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
@@ -760,31 +760,31 @@
         <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>1.233333333333333</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07066666666666667</v>
+        <v>0.06733333333333333</v>
       </c>
       <c r="G2" t="n">
         <v>0.18</v>
       </c>
       <c r="H2" t="n">
-        <v>0.037</v>
+        <v>0.035</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.00445</v>
+        <v>-0.003279999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>-8.666666666666614e-05</v>
+        <v>0.0008466666666666671</v>
       </c>
     </row>
     <row r="3">
@@ -795,28 +795,28 @@
         <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>1.096774193548387</v>
+        <v>1.032258064516129</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0661290322580645</v>
+        <v>0.06290322580645161</v>
       </c>
       <c r="G3" t="n">
         <v>0.18</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03290322580645162</v>
+        <v>0.03096774193548387</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0194</v>
+        <v>0.0180258064516129</v>
       </c>
       <c r="K3" t="n">
         <v>0.0268</v>
@@ -903,28 +903,28 @@
         <v>27</v>
       </c>
       <c r="D6" t="n">
-        <v>3.516129032258065</v>
+        <v>3.32258064516129</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2183870967741935</v>
+        <v>0.2064516129032258</v>
       </c>
       <c r="G6" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06967741935483872</v>
+        <v>0.06387096774193549</v>
       </c>
       <c r="I6" t="n">
         <v>0.01741935483870968</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0132741935483871</v>
+        <v>0.01168064516129032</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01452258064516129</v>
+        <v>0.008387096774193548</v>
       </c>
     </row>
     <row r="7">
@@ -938,28 +938,28 @@
         <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>2.433333333333333</v>
+        <v>2.3</v>
       </c>
       <c r="E7" t="n">
         <v>7</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1446666666666667</v>
+        <v>0.1386666666666667</v>
       </c>
       <c r="G7" t="n">
         <v>0.42</v>
       </c>
       <c r="H7" t="n">
-        <v>0.055</v>
+        <v>0.051</v>
       </c>
       <c r="I7" t="n">
         <v>0.004</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02087</v>
+        <v>0.01986</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01659</v>
+        <v>0.01731333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -973,13 +973,13 @@
         <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>2.064516129032258</v>
+        <v>2.096774193548387</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1309677419354839</v>
+        <v>0.1329032258064516</v>
       </c>
       <c r="G8" t="n">
         <v>0.39</v>
@@ -988,10 +988,10 @@
         <v>0.04548387096774193</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00870967741935484</v>
+        <v>0.00967741935483871</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01201612903225806</v>
+        <v>0.009922580645161289</v>
       </c>
       <c r="K8" t="n">
         <v>0.04107741935483871</v>
@@ -1061,10 +1061,10 @@
         <v>0.01758620689655173</v>
       </c>
       <c r="J10" t="n">
-        <v>0.02075862068965517</v>
+        <v>0.01854827586206897</v>
       </c>
       <c r="K10" t="n">
-        <v>0.009262068965517241</v>
+        <v>0.008972413793103448</v>
       </c>
     </row>
     <row r="11">
@@ -1078,28 +1078,28 @@
         <v>27</v>
       </c>
       <c r="D11" t="n">
-        <v>2.709677419354839</v>
+        <v>2.612903225806452</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1606451612903226</v>
+        <v>0.1564516129032258</v>
       </c>
       <c r="G11" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="H11" t="n">
         <v>0.05419354838709677</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01838709677419355</v>
+        <v>0.01645161290322581</v>
       </c>
       <c r="J11" t="n">
-        <v>0.008783870967741934</v>
+        <v>0.009241935483870967</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0271</v>
+        <v>0.02652258064516129</v>
       </c>
     </row>
     <row r="12">
@@ -1110,31 +1110,31 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6</v>
+        <v>1.433333333333333</v>
       </c>
       <c r="E12" t="n">
         <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08933333333333333</v>
+        <v>0.08033333333333334</v>
       </c>
       <c r="G12" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="H12" t="n">
         <v>0.018</v>
       </c>
       <c r="I12" t="n">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
       <c r="J12" t="n">
-        <v>0.001616666666666667</v>
+        <v>-0.0007466666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.01291</v>
+        <v>-0.01209333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -1183,28 +1183,28 @@
         <v>27</v>
       </c>
       <c r="D14" t="n">
-        <v>1.733333333333333</v>
+        <v>1.6</v>
       </c>
       <c r="E14" t="n">
         <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1086666666666667</v>
+        <v>0.102</v>
       </c>
       <c r="G14" t="n">
         <v>0.32</v>
       </c>
       <c r="H14" t="n">
-        <v>0.044</v>
+        <v>0.04</v>
       </c>
       <c r="I14" t="n">
         <v>0.008</v>
       </c>
       <c r="J14" t="n">
-        <v>0.00667</v>
+        <v>0.004589999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.02898</v>
+        <v>0.02579666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -1218,28 +1218,28 @@
         <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>2.548387096774194</v>
+        <v>2.354838709677419</v>
       </c>
       <c r="E15" t="n">
         <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1474193548387097</v>
+        <v>0.1364516129032258</v>
       </c>
       <c r="G15" t="n">
         <v>0.42</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03870967741935484</v>
+        <v>0.03580645161290322</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02516129032258065</v>
+        <v>0.02225806451612903</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01397096774193548</v>
+        <v>0.01113548387096774</v>
       </c>
       <c r="K15" t="n">
-        <v>0.006051612903225806</v>
+        <v>0.005761290322580644</v>
       </c>
     </row>
     <row r="16">
@@ -1323,13 +1323,13 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>1.870967741935484</v>
+        <v>1.903225806451613</v>
       </c>
       <c r="E18" t="n">
         <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1180645161290323</v>
+        <v>0.1203225806451613</v>
       </c>
       <c r="G18" t="n">
         <v>0.39</v>
@@ -1338,10 +1338,10 @@
         <v>0.03</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01064516129032258</v>
+        <v>0.01161290322580645</v>
       </c>
       <c r="J18" t="n">
-        <v>0.02832258064516129</v>
+        <v>0.0252258064516129</v>
       </c>
       <c r="K18" t="n">
         <v>0.0008903225806451616</v>
@@ -1355,31 +1355,31 @@
         <v>30</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" t="n">
-        <v>2.433333333333333</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="E19" t="n">
         <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1583333333333333</v>
+        <v>0.151</v>
       </c>
       <c r="G19" t="n">
         <v>0.35</v>
       </c>
       <c r="H19" t="n">
-        <v>0.04</v>
+        <v>0.038</v>
       </c>
       <c r="I19" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="J19" t="n">
-        <v>0.03231333333333333</v>
+        <v>0.02292666666666666</v>
       </c>
       <c r="K19" t="n">
-        <v>0.04948666666666666</v>
+        <v>0.03659666666666667</v>
       </c>
     </row>
     <row r="20">
@@ -1411,10 +1411,10 @@
         <v>0.00870967741935484</v>
       </c>
       <c r="J20" t="n">
-        <v>0.001009677419354839</v>
+        <v>0.001032258064516129</v>
       </c>
       <c r="K20" t="n">
-        <v>0.02948064516129032</v>
+        <v>0.02837741935483871</v>
       </c>
     </row>
     <row r="21">
@@ -1460,16 +1460,16 @@
         <v>28</v>
       </c>
       <c r="C22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>1.357142857142857</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="E22" t="n">
         <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08821428571428572</v>
+        <v>0.08428571428571428</v>
       </c>
       <c r="G22" t="n">
         <v>0.22</v>
@@ -1478,7 +1478,7 @@
         <v>0.01928571428571429</v>
       </c>
       <c r="I22" t="n">
-        <v>0.01178571428571428</v>
+        <v>0.009642857142857144</v>
       </c>
       <c r="J22" t="n">
         <v>0.02226428571428571</v>
@@ -1495,28 +1495,28 @@
         <v>31</v>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D23" t="n">
-        <v>1.451612903225806</v>
+        <v>1.483870967741935</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1048387096774194</v>
+        <v>0.1029032258064516</v>
       </c>
       <c r="G23" t="n">
-        <v>0.34</v>
+        <v>0.47</v>
       </c>
       <c r="H23" t="n">
-        <v>0.02516129032258065</v>
+        <v>0.02709677419354839</v>
       </c>
       <c r="I23" t="n">
-        <v>0.000967741935483871</v>
+        <v>0.005806451612903225</v>
       </c>
       <c r="J23" t="n">
-        <v>0.03513225806451613</v>
+        <v>0.02648387096774193</v>
       </c>
       <c r="K23" t="n">
         <v>0.01863548387096774</v>
@@ -1530,16 +1530,16 @@
         <v>30</v>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E24" t="n">
         <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05833333333333333</v>
+        <v>0.054</v>
       </c>
       <c r="G24" t="n">
         <v>0.32</v>
@@ -1548,7 +1548,7 @@
         <v>0.004</v>
       </c>
       <c r="I24" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="J24" t="n">
         <v>0.00333</v>
@@ -1568,28 +1568,28 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>2.548387096774194</v>
+        <v>2.258064516129032</v>
       </c>
       <c r="E25" t="n">
         <v>6</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1525806451612903</v>
+        <v>0.1345161290322581</v>
       </c>
       <c r="G25" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0667741935483871</v>
+        <v>0.05612903225806452</v>
       </c>
       <c r="I25" t="n">
-        <v>0.00870967741935484</v>
+        <v>0.01064516129032258</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.009367741935483872</v>
+        <v>-0.009196774193548387</v>
       </c>
       <c r="K25" t="n">
-        <v>0.002464516129032258</v>
+        <v>-0.01967741935483871</v>
       </c>
     </row>
     <row r="26">
@@ -1638,28 +1638,28 @@
         <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>2.258064516129032</v>
+        <v>2.225806451612903</v>
       </c>
       <c r="E27" t="n">
         <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1416129032258064</v>
+        <v>0.1393548387096774</v>
       </c>
       <c r="G27" t="n">
         <v>0.32</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0532258064516129</v>
+        <v>0.05225806451612903</v>
       </c>
       <c r="I27" t="n">
         <v>0.005806451612903225</v>
       </c>
       <c r="J27" t="n">
-        <v>0.005758064516129032</v>
+        <v>0.005196774193548387</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.006080645161290322</v>
+        <v>-0.006625806451612904</v>
       </c>
     </row>
     <row r="28">
@@ -1708,13 +1708,13 @@
         <v>22</v>
       </c>
       <c r="D29" t="n">
-        <v>1.833333333333333</v>
+        <v>1.8</v>
       </c>
       <c r="E29" t="n">
         <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="G29" t="n">
         <v>0.29</v>
@@ -1723,13 +1723,13 @@
         <v>0.021</v>
       </c>
       <c r="I29" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="J29" t="n">
-        <v>0.01529</v>
+        <v>0.0136</v>
       </c>
       <c r="K29" t="n">
-        <v>0.008766666666666667</v>
+        <v>0.008406666666666666</v>
       </c>
     </row>
     <row r="30">
@@ -1743,13 +1743,13 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>2.741935483870968</v>
+        <v>2.67741935483871</v>
       </c>
       <c r="E30" t="n">
         <v>6</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1648387096774194</v>
+        <v>0.1612903225806452</v>
       </c>
       <c r="G30" t="n">
         <v>0.38</v>
@@ -1761,10 +1761,10 @@
         <v>0.0232258064516129</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.006329032258064517</v>
+        <v>-0.007583870967741936</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.01763548387096774</v>
+        <v>-0.0162258064516129</v>
       </c>
     </row>
     <row r="31">
@@ -1866,7 +1866,7 @@
         <v>0.02225806451612903</v>
       </c>
       <c r="J33" t="n">
-        <v>0.01554838709677419</v>
+        <v>0.01414193548387097</v>
       </c>
       <c r="K33" t="n">
         <v>0.003451612903225807</v>
@@ -1883,13 +1883,13 @@
         <v>25</v>
       </c>
       <c r="D34" t="n">
-        <v>2.964285714285714</v>
+        <v>2.892857142857143</v>
       </c>
       <c r="E34" t="n">
         <v>8</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1703571428571429</v>
+        <v>0.1675</v>
       </c>
       <c r="G34" t="n">
         <v>0.46</v>
@@ -1898,7 +1898,7 @@
         <v>0.05357142857142857</v>
       </c>
       <c r="I34" t="n">
-        <v>0.02892857142857143</v>
+        <v>0.02678571428571428</v>
       </c>
       <c r="J34" t="n">
         <v>0.008946428571428572</v>
@@ -1971,10 +1971,10 @@
         <v>0.012</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02546</v>
+        <v>0.02433333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>0.01342333333333333</v>
+        <v>0.01158333333333333</v>
       </c>
     </row>
     <row r="37">
@@ -2006,10 +2006,10 @@
         <v>0.01258064516129032</v>
       </c>
       <c r="J37" t="n">
-        <v>0.01784193548387097</v>
+        <v>0.01609677419354839</v>
       </c>
       <c r="K37" t="n">
-        <v>0.01735483870967742</v>
+        <v>0.0142258064516129</v>
       </c>
     </row>
     <row r="38">
@@ -2023,28 +2023,28 @@
         <v>28</v>
       </c>
       <c r="D38" t="n">
-        <v>3.482758620689655</v>
+        <v>3.448275862068965</v>
       </c>
       <c r="E38" t="n">
         <v>8</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1827586206896552</v>
+        <v>0.1806896551724138</v>
       </c>
       <c r="G38" t="n">
         <v>0.41</v>
       </c>
       <c r="H38" t="n">
-        <v>0.05586206896551724</v>
+        <v>0.05482758620689655</v>
       </c>
       <c r="I38" t="n">
         <v>0.04448275862068966</v>
       </c>
       <c r="J38" t="n">
-        <v>0.00126551724137931</v>
+        <v>0.002293103448275862</v>
       </c>
       <c r="K38" t="n">
-        <v>0.002451724137931034</v>
+        <v>0.004382758620689655</v>
       </c>
     </row>
   </sheetData>
@@ -2890,19 +2890,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="D21" t="n">
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="E21" t="n">
-        <v>52103</v>
+        <v>23114</v>
       </c>
       <c r="F21" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2911,10 +2911,10 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0215</v>
+        <v>-0.0109</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0306</v>
+        <v>-0.0122</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2936,10 +2936,10 @@
         <v>0.12</v>
       </c>
       <c r="D22" t="n">
-        <v>59838</v>
+        <v>58255</v>
       </c>
       <c r="E22" t="n">
-        <v>58417</v>
+        <v>60000</v>
       </c>
       <c r="F22" t="n">
         <v>0.06</v>
@@ -2951,10 +2951,10 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0048</v>
+        <v>0.024</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0033</v>
+        <v>0.0343</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -3359,7 +3359,7 @@
         <v>45078</v>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -3403,10 +3403,10 @@
         <v>45200</v>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3414,7 +3414,7 @@
         <v>45231</v>
       </c>
       <c r="B7" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
         <v>45261</v>
       </c>
       <c r="B8" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>45323</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -3458,7 +3458,7 @@
         <v>45352</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
         <v>2</v>
@@ -3469,7 +3469,7 @@
         <v>45383</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -3491,7 +3491,7 @@
         <v>45444</v>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -3502,10 +3502,10 @@
         <v>45474</v>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3535,7 +3535,7 @@
         <v>45566</v>
       </c>
       <c r="B18" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>45597</v>
       </c>
       <c r="B19" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -3557,7 +3557,7 @@
         <v>45627</v>
       </c>
       <c r="B20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -3590,7 +3590,7 @@
         <v>45717</v>
       </c>
       <c r="B23" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -3601,7 +3601,7 @@
         <v>45748</v>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -3612,7 +3612,7 @@
         <v>45778</v>
       </c>
       <c r="B25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -3634,10 +3634,10 @@
         <v>45839</v>
       </c>
       <c r="B27" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3656,7 +3656,7 @@
         <v>45901</v>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -3667,7 +3667,7 @@
         <v>45931</v>
       </c>
       <c r="B30" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
         <v>46023</v>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -3711,7 +3711,7 @@
         <v>46113</v>
       </c>
       <c r="B34" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -3722,7 +3722,7 @@
         <v>46143</v>
       </c>
       <c r="B35" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
